--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_15_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_15_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-80318.931435633</v>
+        <v>-80316.5748787029</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26023845.20571312</v>
+        <v>26027291.21166012</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2101854.566364616</v>
+        <v>2100334.594240383</v>
       </c>
     </row>
     <row r="11">
@@ -23230,49 +23230,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H11" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I11" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J11" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K11" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L11" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M11" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N11" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O11" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P11" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q11" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R11" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S11" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T11" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U11" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,22 +23309,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H12" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I12" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J12" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K12" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L12" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -23333,25 +23333,25 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P12" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q12" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R12" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S12" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T12" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,49 +23388,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H13" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I13" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J13" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K13" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L13" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M13" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N13" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O13" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P13" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q13" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R13" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S13" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T13" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,49 +23467,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H14" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I14" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J14" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K14" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L14" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M14" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N14" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O14" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P14" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q14" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R14" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S14" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T14" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U14" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,22 +23546,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H15" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I15" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J15" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K15" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L15" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -23570,25 +23570,25 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P15" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q15" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R15" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S15" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T15" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,49 +23625,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H16" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I16" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J16" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K16" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L16" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M16" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N16" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O16" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P16" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q16" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R16" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S16" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T16" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,49 +23704,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H17" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I17" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J17" t="n">
-        <v>91.99244221512849</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K17" t="n">
-        <v>86.62179576859862</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L17" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M17" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N17" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O17" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P17" t="n">
-        <v>80.35007615727957</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R17" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S17" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T17" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U17" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,22 +23783,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H18" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I18" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J18" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K18" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L18" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -23807,25 +23807,25 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P18" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q18" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R18" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S18" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T18" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,49 +23862,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H19" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I19" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J19" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K19" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L19" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M19" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N19" t="n">
-        <v>55.66238053080691</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O19" t="n">
-        <v>71.93148927151489</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P19" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q19" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R19" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S19" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T19" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,49 +23941,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H20" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I20" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J20" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K20" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L20" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M20" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N20" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O20" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P20" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q20" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R20" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S20" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T20" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U20" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,22 +24020,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H21" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I21" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J21" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K21" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L21" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -24044,25 +24044,25 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P21" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q21" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R21" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S21" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T21" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,49 +24099,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H22" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I22" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J22" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K22" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L22" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M22" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N22" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O22" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P22" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q22" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R22" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S22" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T22" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,49 +24178,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H23" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I23" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J23" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K23" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L23" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M23" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N23" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O23" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P23" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q23" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R23" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S23" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T23" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U23" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,22 +24257,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H24" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I24" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J24" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K24" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L24" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -24281,25 +24281,25 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P24" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q24" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R24" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S24" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T24" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,49 +24336,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H25" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I25" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J25" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K25" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L25" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M25" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N25" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O25" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P25" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q25" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R25" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S25" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T25" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,49 +24415,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H26" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I26" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J26" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K26" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L26" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M26" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N26" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O26" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P26" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q26" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R26" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S26" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T26" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U26" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,22 +24494,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H27" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I27" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J27" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K27" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L27" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -24518,25 +24518,25 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P27" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q27" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R27" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S27" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T27" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,49 +24573,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H28" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I28" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J28" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K28" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L28" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M28" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N28" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O28" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P28" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q28" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R28" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S28" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T28" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,49 +24652,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H29" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I29" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J29" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K29" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L29" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M29" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N29" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O29" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P29" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q29" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R29" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S29" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T29" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U29" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,22 +24731,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H30" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I30" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J30" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K30" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L30" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -24755,25 +24755,25 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P30" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q30" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R30" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S30" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T30" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,49 +24810,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H31" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I31" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J31" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K31" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L31" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M31" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N31" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O31" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P31" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q31" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R31" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S31" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T31" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,49 +24889,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H32" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I32" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J32" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K32" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L32" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M32" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N32" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O32" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P32" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q32" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R32" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S32" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T32" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U32" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,22 +24968,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H33" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I33" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J33" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K33" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L33" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -24992,25 +24992,25 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P33" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q33" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R33" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S33" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T33" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,49 +25047,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H34" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I34" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J34" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K34" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L34" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M34" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N34" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O34" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P34" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q34" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R34" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S34" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T34" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,49 +25126,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H35" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I35" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J35" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K35" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L35" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M35" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N35" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O35" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P35" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q35" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R35" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S35" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T35" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U35" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,22 +25205,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H36" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I36" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J36" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K36" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L36" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -25229,25 +25229,25 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P36" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q36" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R36" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S36" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T36" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,49 +25284,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H37" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I37" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J37" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K37" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L37" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M37" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N37" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O37" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P37" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q37" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R37" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S37" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T37" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,49 +25363,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H38" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I38" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J38" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K38" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L38" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M38" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N38" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O38" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P38" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q38" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R38" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S38" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T38" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U38" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,22 +25442,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H39" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I39" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J39" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K39" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L39" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -25466,25 +25466,25 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P39" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q39" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R39" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S39" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T39" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,49 +25521,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H40" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I40" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J40" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K40" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L40" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M40" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N40" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O40" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P40" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q40" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R40" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S40" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T40" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,49 +25600,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H41" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I41" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J41" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280013</v>
       </c>
       <c r="K41" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L41" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M41" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729366</v>
       </c>
       <c r="N41" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O41" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P41" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q41" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R41" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629756</v>
       </c>
       <c r="S41" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T41" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U41" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,22 +25679,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H42" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I42" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J42" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913169</v>
       </c>
       <c r="K42" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L42" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -25703,25 +25703,25 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P42" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q42" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R42" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S42" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T42" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,49 +25758,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H43" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I43" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J43" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K43" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L43" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M43" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N43" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O43" t="n">
-        <v>71.93148927151491</v>
+        <v>71.9833858147683</v>
       </c>
       <c r="P43" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615827</v>
       </c>
       <c r="Q43" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R43" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S43" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T43" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,49 +25837,49 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.2534912839793</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H44" t="n">
-        <v>328.729209150943</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I44" t="n">
-        <v>170.0248242437727</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J44" t="n">
-        <v>91.99244221512848</v>
+        <v>92.06191329280011</v>
       </c>
       <c r="K44" t="n">
-        <v>86.62179576859864</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L44" t="n">
-        <v>70.18749034687164</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M44" t="n">
-        <v>46.10777594084058</v>
+        <v>46.25150133729363</v>
       </c>
       <c r="N44" t="n">
-        <v>42.1934354558874</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O44" t="n">
-        <v>53.31202549203849</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P44" t="n">
-        <v>80.3500761572796</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q44" t="n">
-        <v>108.9989009297259</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R44" t="n">
-        <v>149.6758242462929</v>
+        <v>149.7272407629755</v>
       </c>
       <c r="S44" t="n">
-        <v>185.110371093783</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T44" t="n">
-        <v>218.5027741872469</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U44" t="n">
-        <v>251.261713209344</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,22 +25916,22 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.7821209367955</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H45" t="n">
-        <v>106.8135385761191</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I45" t="n">
-        <v>80.19360641509434</v>
+        <v>80.20868489375378</v>
       </c>
       <c r="J45" t="n">
-        <v>73.79799459119499</v>
+        <v>73.83937108913167</v>
       </c>
       <c r="K45" t="n">
-        <v>47.18825972907597</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L45" t="n">
-        <v>16.65999298742133</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -25940,25 +25940,25 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>9.025801048218028</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P45" t="n">
-        <v>26.77235081055665</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q45" t="n">
-        <v>68.3200382369649</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R45" t="n">
-        <v>110.8236926432092</v>
+        <v>110.8508838462542</v>
       </c>
       <c r="S45" t="n">
-        <v>161.2554824245925</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T45" t="n">
-        <v>197.9019079401046</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9044481187107</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,49 +25995,49 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.5203236207538</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H46" t="n">
-        <v>158.0426151303904</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I46" t="n">
-        <v>141.296573287914</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J46" t="n">
-        <v>93.72006078365841</v>
+        <v>93.74601906876785</v>
       </c>
       <c r="K46" t="n">
-        <v>74.3316188262731</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L46" t="n">
-        <v>64.91100415009073</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M46" t="n">
-        <v>65.14835771809688</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N46" t="n">
-        <v>55.66238053080693</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O46" t="n">
-        <v>71.93148927151491</v>
+        <v>71.98338581476828</v>
       </c>
       <c r="P46" t="n">
-        <v>80.8043319180001</v>
+        <v>80.84873837615825</v>
       </c>
       <c r="Q46" t="n">
-        <v>112.0940016294458</v>
+        <v>112.1247463593087</v>
       </c>
       <c r="R46" t="n">
-        <v>156.1309979345465</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S46" t="n">
-        <v>215.8143521353329</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T46" t="n">
-        <v>225.9346058217241</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2933572253434</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777343</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>242232.075846706</v>
+        <v>242056.9038777344</v>
       </c>
     </row>
   </sheetData>
@@ -26270,40 +26270,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>35739.15873148122</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="F2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687885</v>
       </c>
       <c r="G2" t="n">
-        <v>35739.15873148122</v>
+        <v>35713.31368687885</v>
       </c>
       <c r="H2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="I2" t="n">
-        <v>35739.15873148122</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="J2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="K2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="L2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="M2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="N2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="O2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
       <c r="P2" t="n">
-        <v>35739.15873148121</v>
+        <v>35713.31368687886</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>209688.183</v>
+        <v>209524.6041377088</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="F5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="G5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="H5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="I5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="J5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="K5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="L5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="M5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="N5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="O5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
       <c r="P5" t="n">
-        <v>5689.8</v>
+        <v>5685.361356880733</v>
       </c>
     </row>
     <row r="6">
@@ -26478,40 +26478,40 @@
         <v>-33627.6</v>
       </c>
       <c r="E6" t="n">
-        <v>-179638.8242685188</v>
+        <v>-179496.6518077107</v>
       </c>
       <c r="F6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="G6" t="n">
-        <v>30049.35873148122</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="H6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="I6" t="n">
-        <v>30049.35873148122</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="J6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="K6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="L6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="M6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="N6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="O6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
       <c r="P6" t="n">
-        <v>30049.35873148121</v>
+        <v>30027.95232999812</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="F3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="G3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="H3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="I3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="J3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="K3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="L3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="M3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="N3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="O3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="P3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
     </row>
     <row r="4">
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I11" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J11" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K11" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L11" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M11" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N11" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O11" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P11" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q11" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R11" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S11" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T11" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H12" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I12" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J12" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K12" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L12" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M12" t="n">
-        <v>142.1340339220186</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P12" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q12" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R12" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S12" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T12" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H13" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I13" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J13" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K13" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L13" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M13" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N13" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O13" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P13" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q13" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R13" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S13" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T13" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I14" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J14" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K14" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L14" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M14" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N14" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O14" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P14" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q14" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R14" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S14" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T14" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,22 +31986,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H15" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I15" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J15" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K15" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L15" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -32010,25 +32010,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P15" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q15" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R15" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S15" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T15" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H16" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I16" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J16" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K16" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L16" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M16" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N16" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O16" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P16" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R16" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S16" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T16" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H17" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I17" t="n">
-        <v>40.45106532663317</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J17" t="n">
-        <v>89.05346231155779</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K17" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L17" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M17" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N17" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O17" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P17" t="n">
-        <v>150.88291959799</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q17" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R17" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S17" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T17" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,22 +32223,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H18" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I18" t="n">
-        <v>19.32877358490567</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J18" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K18" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L18" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -32247,25 +32247,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P18" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q18" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R18" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S18" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T18" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H19" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I19" t="n">
-        <v>14.15390163934426</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J19" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K19" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L19" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M19" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N19" t="n">
-        <v>72.02316393442628</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O19" t="n">
-        <v>66.5250491803279</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P19" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R19" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S19" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T19" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U19" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H20" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I20" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J20" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K20" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L20" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M20" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N20" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O20" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P20" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q20" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R20" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S20" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T20" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,22 +32460,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H21" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I21" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J21" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K21" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L21" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -32484,25 +32484,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P21" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q21" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R21" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S21" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T21" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U21" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H22" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I22" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J22" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K22" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L22" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M22" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N22" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O22" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P22" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q22" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R22" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S22" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T22" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H23" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I23" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J23" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K23" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L23" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M23" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N23" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O23" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P23" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R23" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S23" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T23" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,22 +32697,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H24" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I24" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J24" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K24" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L24" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -32721,25 +32721,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P24" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q24" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R24" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S24" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T24" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U24" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H25" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I25" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J25" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K25" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L25" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M25" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N25" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O25" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P25" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R25" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S25" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T25" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H26" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I26" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J26" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K26" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L26" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M26" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N26" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O26" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P26" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q26" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R26" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S26" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T26" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,22 +32934,22 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H27" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I27" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J27" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K27" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L27" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -32958,25 +32958,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P27" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q27" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R27" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S27" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T27" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U27" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H28" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I28" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J28" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K28" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L28" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M28" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N28" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O28" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P28" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q28" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R28" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S28" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T28" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H29" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I29" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J29" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K29" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L29" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M29" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N29" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O29" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P29" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q29" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R29" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S29" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T29" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U29" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,22 +33171,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H30" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I30" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J30" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K30" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L30" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
@@ -33195,25 +33195,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P30" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q30" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R30" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S30" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T30" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U30" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H31" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I31" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J31" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K31" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L31" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M31" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N31" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O31" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P31" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q31" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R31" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S31" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T31" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H32" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I32" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J32" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K32" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L32" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M32" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N32" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O32" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P32" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q32" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R32" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S32" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T32" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,22 +33408,22 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H33" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I33" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J33" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K33" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L33" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -33432,25 +33432,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P33" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q33" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R33" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S33" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T33" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U33" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H34" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I34" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J34" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K34" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L34" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M34" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N34" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O34" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P34" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q34" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R34" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S34" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T34" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H35" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I35" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J35" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K35" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L35" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M35" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N35" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O35" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P35" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q35" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R35" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S35" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T35" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,22 +33645,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H36" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I36" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J36" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K36" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L36" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
@@ -33669,25 +33669,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P36" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q36" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R36" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S36" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T36" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U36" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H37" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I37" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J37" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K37" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L37" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M37" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N37" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O37" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P37" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q37" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R37" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S37" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T37" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H38" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I38" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J38" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K38" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L38" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M38" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N38" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O38" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P38" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q38" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R38" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S38" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T38" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,22 +33882,22 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H39" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I39" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J39" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K39" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L39" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
@@ -33906,25 +33906,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P39" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R39" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S39" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T39" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H40" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I40" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J40" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K40" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L40" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M40" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N40" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O40" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P40" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q40" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R40" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S40" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T40" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H41" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I41" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J41" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388616</v>
       </c>
       <c r="K41" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L41" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M41" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N41" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O41" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P41" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q41" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R41" t="n">
-        <v>65.9097135678392</v>
+        <v>65.85829705115658</v>
       </c>
       <c r="S41" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T41" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U41" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903383</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,22 +34119,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H42" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051487</v>
       </c>
       <c r="I42" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J42" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K42" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L42" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
@@ -34143,25 +34143,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P42" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q42" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R42" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S42" t="n">
-        <v>10.42768867924528</v>
+        <v>10.4195539840704</v>
       </c>
       <c r="T42" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U42" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H43" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I43" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J43" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062825</v>
       </c>
       <c r="K43" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L43" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M43" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N43" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O43" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707449</v>
       </c>
       <c r="P43" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298935</v>
       </c>
       <c r="Q43" t="n">
-        <v>39.411</v>
+        <v>39.38025527013718</v>
       </c>
       <c r="R43" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S43" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T43" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U43" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.049246231155778</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H44" t="n">
-        <v>10.74559296482412</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I44" t="n">
-        <v>40.45106532663318</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J44" t="n">
-        <v>89.05346231155781</v>
+        <v>88.98399123388617</v>
       </c>
       <c r="K44" t="n">
-        <v>133.4680552763819</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L44" t="n">
-        <v>165.5789246231156</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M44" t="n">
-        <v>184.2384572864322</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N44" t="n">
-        <v>187.2196281407035</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O44" t="n">
-        <v>176.7861859296482</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P44" t="n">
-        <v>150.8829195979899</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q44" t="n">
-        <v>113.3067889447236</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R44" t="n">
-        <v>65.9097135678392</v>
+        <v>65.8582970511566</v>
       </c>
       <c r="S44" t="n">
-        <v>23.90969849246232</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T44" t="n">
-        <v>4.593075376884421</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08393969849246223</v>
+        <v>0.08387421668903385</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,22 +34356,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5613962264150943</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H45" t="n">
-        <v>5.42190566037736</v>
+        <v>5.417676003051488</v>
       </c>
       <c r="I45" t="n">
-        <v>19.32877358490566</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J45" t="n">
-        <v>53.03963207547171</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K45" t="n">
-        <v>90.65317924528303</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L45" t="n">
-        <v>121.8943867924528</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M45" t="n">
         <v>142.1340339220183</v>
@@ -34380,25 +34380,25 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>133.5704433962264</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P45" t="n">
-        <v>107.2020566037736</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q45" t="n">
-        <v>71.66173584905661</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R45" t="n">
-        <v>34.85581132075473</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S45" t="n">
-        <v>10.42768867924528</v>
+        <v>10.41955398407041</v>
       </c>
       <c r="T45" t="n">
-        <v>2.262820754716981</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U45" t="n">
-        <v>0.03693396226415096</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.470655737704918</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H46" t="n">
-        <v>4.184557377049183</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I46" t="n">
-        <v>14.15390163934427</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J46" t="n">
-        <v>33.2753606557377</v>
+        <v>33.24940237062826</v>
       </c>
       <c r="K46" t="n">
-        <v>54.68163934426228</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L46" t="n">
-        <v>69.97367213114755</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M46" t="n">
-        <v>73.77742622950818</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N46" t="n">
-        <v>72.02316393442626</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O46" t="n">
-        <v>66.52504918032788</v>
+        <v>66.47315263707451</v>
       </c>
       <c r="P46" t="n">
-        <v>56.92367213114751</v>
+        <v>56.87926567298936</v>
       </c>
       <c r="Q46" t="n">
-        <v>39.411</v>
+        <v>39.38025527013719</v>
       </c>
       <c r="R46" t="n">
-        <v>21.16239344262294</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S46" t="n">
-        <v>8.202245901639341</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T46" t="n">
-        <v>2.010983606557376</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U46" t="n">
-        <v>0.02567213114754101</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
